--- a/data/trans_dic/IP12_R1_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023</t>
+          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,0; 5,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,54</t>
+          <t>1,2; 3,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,67</t>
+          <t>1,35; 3,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,16</t>
+          <t>1,49; 3,18</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,13</t>
+          <t>0,99; 5,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,66</t>
+          <t>0,73; 3,53</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,3</t>
+          <t>1,39; 3,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,82</t>
+          <t>1,08; 2,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,65</t>
+          <t>1,41; 2,72</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3233</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2768</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10088</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11641</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21729</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5522; 15660</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6989; 19593</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14511; 31034</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3799</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1927</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5726</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1483; 8701</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 6135</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2439; 11744</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>14721</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13568</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>28290</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>9260; 22226</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8264; 21555</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>20149; 38833</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12_R1_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,91</t>
+          <t>0,0; 6,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,41</t>
+          <t>1,26; 3,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,79</t>
+          <t>1,27; 3,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,18</t>
+          <t>1,51; 3,26</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,82</t>
+          <t>0,92; 5,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,35</t>
+          <t>0,0; 3,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,53</t>
+          <t>0,78; 3,45</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,35</t>
+          <t>1,42; 3,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,83</t>
+          <t>1,03; 2,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,72</t>
+          <t>1,45; 2,75</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3233</t>
+          <t>0; 3292</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2768</t>
+          <t>0; 3059</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5522; 15660</t>
+          <t>5813; 15943</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6989; 19593</t>
+          <t>6548; 19113</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14511; 31034</t>
+          <t>14765; 31841</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1483; 8701</t>
+          <t>1380; 8557</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6135</t>
+          <t>0; 6450</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2439; 11744</t>
+          <t>2599; 11492</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9260; 22226</t>
+          <t>9405; 21945</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8264; 21555</t>
+          <t>7886; 21745</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20149; 38833</t>
+          <t>20648; 39177</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R1_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,47</t>
+          <t>1,35; 3,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,7</t>
+          <t>1,32; 3,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,26</t>
+          <t>1,63; 3,37</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,72</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,52</t>
+          <t>0,99; 6,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,45</t>
+          <t>0,82; 3,85</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,31</t>
+          <t>1,14; 2,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,85</t>
+          <t>1,46; 3,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,75</t>
+          <t>1,48; 2,82</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>725</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>725</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3292</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3008</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3059</t>
+          <t>0; 2303</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10088</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21729</t>
+          <t>21338</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5813; 15943</t>
+          <t>6429; 18635</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6548; 19113</t>
+          <t>5684; 16375</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14765; 31841</t>
+          <t>14755; 30580</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5722</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1380; 8557</t>
+          <t>0; 5640</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6450</t>
+          <t>1480; 9570</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2599; 11492</t>
+          <t>2602; 12252</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>14659</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>27785</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9405; 21945</t>
+          <t>7972; 20665</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7886; 21745</t>
+          <t>9182; 22309</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20648; 39177</t>
+          <t>19686; 37443</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R1_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,43</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,23</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,35; 3,92</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,32; 3,79</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,63; 3,37</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,35</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,99; 6,38</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,82; 3,85</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,14; 2,95</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,46; 3,55</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,48; 2,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,47 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.01550713045687556</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.007006256272338284</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3008</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2303</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>0.0643384761337311</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.02225634444383095</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +603,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.02371519164895862</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.02330165088972136</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.02351846635154423</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>11281</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10057</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21338</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.01351510550327154</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.01316885237957285</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.01626278955062838</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6429; 18635</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5684; 16375</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>14755; 30580</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.03917521491679345</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.03793938007294707</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.03370493164174135</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +658,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.01095908278271512</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.0258476974428074</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.01797219652375111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1846</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3877</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5722</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.009870787959643468</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.008171613058012884</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0; 5640</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1480; 9570</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2602; 12252</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.03348982716787453</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.06381111835971665</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.03848156079149526</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.01872997507157947</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.02332933119513591</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.02090422750178996</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>13127</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>14659</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>27785</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.01137457475397697</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.01461282807744578</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.01481110459952923</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>7972; 20665</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9182; 22309</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>19686; 37443</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.02948654580432733</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.03550458751798925</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.02817031502667698</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +777,372 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>725</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="n">
+        <v>3008</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>11281</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>10057</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>21338</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>6429</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>5684</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>14755</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>18635</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>16375</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>30580</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1846</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>3877</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>5722</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1480</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>2602</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>5640</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>9570</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>12252</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>13127</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>14659</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>27785</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>7972</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>9182</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>19686</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>20665</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>22309</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>37443</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>